--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF1491FD-7AD2-4EE3-9A83-3FFDD53899B2}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99571D42-E43F-41EF-BFED-A87BB83CC223}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
   <sheets>
     <sheet name="ICP" sheetId="1" r:id="rId1"/>
@@ -2910,6 +2910,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840A9CD1-4073-4C0E-BD17-8AA10D639CAA}">
   <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2936,7 +2941,7 @@
         <v>151</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2950,7 +2955,7 @@
         <v>152</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2964,7 +2969,7 @@
         <v>153</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2978,7 +2983,7 @@
         <v>154</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2992,7 +2997,7 @@
         <v>155</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3006,7 +3011,7 @@
         <v>156</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3020,7 +3025,7 @@
         <v>157</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3090,7 +3095,7 @@
         <v>162</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3104,7 +3109,7 @@
         <v>163</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3118,7 +3123,7 @@
         <v>164</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3132,7 +3137,7 @@
         <v>165</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3146,7 +3151,7 @@
         <v>166</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3160,7 +3165,7 @@
         <v>167</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3174,7 +3179,7 @@
         <v>168</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3188,7 +3193,7 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3202,7 +3207,7 @@
         <v>170</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3216,7 +3221,7 @@
         <v>171</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3230,7 +3235,7 @@
         <v>172</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3244,7 +3249,7 @@
         <v>173</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3258,7 +3263,7 @@
         <v>174</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3272,7 +3277,7 @@
         <v>175</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3286,7 +3291,7 @@
         <v>176</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3300,7 +3305,7 @@
         <v>177</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3314,7 +3319,7 @@
         <v>178</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3328,7 +3333,7 @@
         <v>179</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3342,7 +3347,7 @@
         <v>180</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3356,7 +3361,7 @@
         <v>181</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3370,7 +3375,7 @@
         <v>182</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3384,7 +3389,7 @@
         <v>183</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3398,7 +3403,7 @@
         <v>184</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3412,7 +3417,7 @@
         <v>185</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3426,7 +3431,7 @@
         <v>186</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3440,7 +3445,7 @@
         <v>187</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99571D42-E43F-41EF-BFED-A87BB83CC223}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50A5AEB1-00B2-42D9-8776-CBEA6D22DE63}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
@@ -2941,7 +2941,7 @@
         <v>151</v>
       </c>
       <c r="D2">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>152</v>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2969,7 +2969,7 @@
         <v>153</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,7 +2983,7 @@
         <v>154</v>
       </c>
       <c r="D5">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2997,7 +2997,7 @@
         <v>155</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3011,7 +3011,7 @@
         <v>156</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3025,7 +3025,7 @@
         <v>157</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3039,7 +3039,7 @@
         <v>158</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3053,7 +3053,7 @@
         <v>159</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3067,7 +3067,7 @@
         <v>160</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3081,7 +3081,7 @@
         <v>161</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3095,7 +3095,7 @@
         <v>162</v>
       </c>
       <c r="D13">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3109,7 +3109,7 @@
         <v>163</v>
       </c>
       <c r="D14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3123,7 +3123,7 @@
         <v>164</v>
       </c>
       <c r="D15">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3137,7 +3137,7 @@
         <v>165</v>
       </c>
       <c r="D16">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3151,7 +3151,7 @@
         <v>166</v>
       </c>
       <c r="D17">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3165,7 +3165,7 @@
         <v>167</v>
       </c>
       <c r="D18">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3179,7 +3179,7 @@
         <v>168</v>
       </c>
       <c r="D19">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,7 +3193,7 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3207,7 +3207,7 @@
         <v>170</v>
       </c>
       <c r="D21">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3221,7 +3221,7 @@
         <v>171</v>
       </c>
       <c r="D22">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3235,7 +3235,7 @@
         <v>172</v>
       </c>
       <c r="D23">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3249,7 +3249,7 @@
         <v>173</v>
       </c>
       <c r="D24">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3263,7 +3263,7 @@
         <v>174</v>
       </c>
       <c r="D25">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3277,7 +3277,7 @@
         <v>175</v>
       </c>
       <c r="D26">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3291,7 +3291,7 @@
         <v>176</v>
       </c>
       <c r="D27">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3305,7 +3305,7 @@
         <v>177</v>
       </c>
       <c r="D28">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3319,7 +3319,7 @@
         <v>178</v>
       </c>
       <c r="D29">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3333,7 +3333,7 @@
         <v>179</v>
       </c>
       <c r="D30">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3347,7 +3347,7 @@
         <v>180</v>
       </c>
       <c r="D31">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
         <v>181</v>
       </c>
       <c r="D32">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3375,7 +3375,7 @@
         <v>182</v>
       </c>
       <c r="D33">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3389,7 +3389,7 @@
         <v>183</v>
       </c>
       <c r="D34">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3403,7 +3403,7 @@
         <v>184</v>
       </c>
       <c r="D35">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3417,7 +3417,7 @@
         <v>185</v>
       </c>
       <c r="D36">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3431,7 +3431,7 @@
         <v>186</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3445,7 +3445,7 @@
         <v>187</v>
       </c>
       <c r="D38">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50A5AEB1-00B2-42D9-8776-CBEA6D22DE63}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8B189C-9F57-4744-832B-472934676DEB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="custos_adm" sheetId="3" r:id="rId3"/>
     <sheet name="custos_pessoal" sheetId="4" r:id="rId4"/>
     <sheet name="tempo_pessoas" sheetId="5" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="196">
   <si>
     <t>Nota</t>
   </si>
@@ -625,6 +626,9 @@
   </si>
   <si>
     <t>Muito alta complexidade</t>
+  </si>
+  <si>
+    <t>1h</t>
   </si>
 </sst>
 </file>
@@ -2941,7 +2945,7 @@
         <v>151</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2955,7 +2959,7 @@
         <v>152</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2969,7 +2973,7 @@
         <v>153</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,7 +2987,7 @@
         <v>154</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2997,7 +3001,7 @@
         <v>155</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3025,7 +3029,7 @@
         <v>157</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3039,7 +3043,7 @@
         <v>158</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3053,7 +3057,7 @@
         <v>159</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3067,7 +3071,7 @@
         <v>160</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3081,7 +3085,7 @@
         <v>161</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3095,7 +3099,7 @@
         <v>162</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3109,7 +3113,7 @@
         <v>163</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3123,7 +3127,7 @@
         <v>164</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3137,7 +3141,7 @@
         <v>165</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3165,7 +3169,7 @@
         <v>167</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3179,7 +3183,7 @@
         <v>168</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,7 +3197,7 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3221,7 +3225,7 @@
         <v>171</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3235,7 +3239,7 @@
         <v>172</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3249,7 +3253,7 @@
         <v>173</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3263,7 +3267,7 @@
         <v>174</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3277,7 +3281,7 @@
         <v>175</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3291,7 +3295,7 @@
         <v>176</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3305,7 +3309,7 @@
         <v>177</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3319,7 +3323,7 @@
         <v>178</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3333,7 +3337,7 @@
         <v>179</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3361,7 +3365,7 @@
         <v>181</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3375,7 +3379,7 @@
         <v>182</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3389,7 +3393,7 @@
         <v>183</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3403,7 +3407,7 @@
         <v>184</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3417,7 +3421,7 @@
         <v>185</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3431,7 +3435,7 @@
         <v>186</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3445,7 +3449,535 @@
         <v>187</v>
       </c>
       <c r="D38">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22950D24-331F-4E79-8529-0D3CDDF13F2D}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8B189C-9F57-4744-832B-472934676DEB}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65321EE5-4A7C-4122-8CA2-C23C39D35C93}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
@@ -2987,7 +2987,7 @@
         <v>154</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3015,7 +3015,7 @@
         <v>156</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>158</v>
       </c>
       <c r="D9">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3057,7 +3057,7 @@
         <v>159</v>
       </c>
       <c r="D10">
-        <v>0.35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3071,7 +3071,7 @@
         <v>160</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3085,7 +3085,7 @@
         <v>161</v>
       </c>
       <c r="D12">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3113,7 +3113,7 @@
         <v>163</v>
       </c>
       <c r="D14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3127,7 +3127,7 @@
         <v>164</v>
       </c>
       <c r="D15">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3183,7 +3183,7 @@
         <v>168</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3197,7 +3197,7 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3211,7 +3211,7 @@
         <v>170</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3323,7 +3323,7 @@
         <v>178</v>
       </c>
       <c r="D29">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3337,7 +3337,7 @@
         <v>179</v>
       </c>
       <c r="D30">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3351,7 +3351,7 @@
         <v>180</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3449,7 +3449,7 @@
         <v>187</v>
       </c>
       <c r="D38">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65321EE5-4A7C-4122-8CA2-C23C39D35C93}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B779B8AF-E235-461D-B0E0-C7CDC181ABEC}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>151</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2959,7 +2959,7 @@
         <v>152</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2973,7 +2973,7 @@
         <v>153</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3197,7 +3197,7 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3351,7 +3351,7 @@
         <v>180</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">

--- a/dados/custos_indicadores.xlsx
+++ b/dados/custos_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://factofundacao-my.sharepoint.com/personal/katarina_lemos_facto_org_br/Documents/Área de Trabalho/my_codes/precificacao_doa/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B779B8AF-E235-461D-B0E0-C7CDC181ABEC}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{06238C4E-BBDD-4287-A41D-A1D766E44EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D188E989-BB0A-4DD9-9EA3-8BA39031EB73}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3260332E-0F91-4634-B5BE-37CAFC126351}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="198">
   <si>
     <t>Nota</t>
   </si>
@@ -629,6 +629,12 @@
   </si>
   <si>
     <t>1h</t>
+  </si>
+  <si>
+    <t>Contratação de RPA (PS/Concurso)</t>
+  </si>
+  <si>
+    <t>Contratação de RPA (Projetos)</t>
   </si>
 </sst>
 </file>
@@ -3194,7 +3200,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D20">
         <v>1.5</v>
@@ -3334,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D30">
         <v>4</v>
